--- a/output/Python/DeepSeek-V3/task_analysis_results_singlepass_Python_DeepSeek-V3_zebralogic.xlsx
+++ b/output/Python/DeepSeek-V3/task_analysis_results_singlepass_Python_DeepSeek-V3_zebralogic.xlsx
@@ -1452,7 +1452,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G98"/>
+  <dimension ref="A1:G101"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1506,169 +1506,105 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E2" t="b">
+        <v>1</v>
+      </c>
+      <c r="F2" t="b">
+        <v>1</v>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Hobby", "Height", "Food"], "rows": [["1", "Peter", "knitting", "short", "spaghetti"], ["2", "Eric", "painting", "very tall", "stew"], ["3", "Bob", "photography", "tall", "grilled cheese"], ["4", "Alice", "cooking", "average", "stir fry"], ["5", "Arnold", "gardening", "very short", "pizza"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x6-20</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" t="b">
+        <v>1</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E3" t="b">
+        <v>0</v>
+      </c>
+      <c r="F3" t="b">
+        <v>0</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Traceback (most recent call last):
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 00:19:32.py", line 244, in &lt;module&gt;
+    print(solve_puzzle())
+          ^^^^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 00:19:32.py", line 155, in solve_puzzle
+    if assignment[pos]['Mother'] == 'Kailyn':
+       ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+KeyboardInterrupt</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x6-26</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="b">
+        <v>0</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
           <t>Wrong plan</t>
         </is>
       </c>
-      <c r="E2" t="b">
-        <v>0</v>
-      </c>
-      <c r="F2" t="b">
-        <v>0</v>
-      </c>
-      <c r="G2" t="inlineStr">
+      <c r="E4" t="b">
+        <v>0</v>
+      </c>
+      <c r="F4" t="b">
+        <v>0</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Hobby",
-      "Height",
-      "Lunch"
-    ],
-    "rows": [
-      [
-        "1",
-        "Peter",
-        "knitting",
-        "short",
-        "spaghetti"
-      ],
-      [
-        "2",
-        "Eric",
-        "painting",
-        "very tall",
-        "stew"
-      ],
-      [
-        "3",
-        "Bob",
-        "photography",
-        "tall",
-        "grilled cheese"
-      ],
-      [
-        "4",
-        "Alice",
-        "cooking",
-        "average",
-        "stir fry"
-      ],
-      [
-        "5",
-        "Arnold",
-        "gardening",
-        "very short",
-        "pizza"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x6-20</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" t="b">
-        <v>1</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E3" t="b">
-        <v>0</v>
-      </c>
-      <c r="F3" t="b">
-        <v>0</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:30:46.py", line 163, in &lt;module&gt;
-    solution = solve_puzzle()
-               ^^^^^^^^^^^^^^
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:30:46.py", line 23, in solve_puzzle
-    from constraint import Problem, AllDifferentConstraint
-ModuleNotFoundError: No module named 'constraint'</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x6-26</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" t="b">
-        <v>0</v>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E4" t="b">
-        <v>0</v>
-      </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "Phone",
+      "PhoneModel",
       "Cigar",
       "Flower",
       "Color",
-      "Sport"
+      "FavoriteSport"
     ],
     "rows": [
       [
         "1",
         "Alice",
         "samsung galaxy s21",
-        "yellow monster",
+        "blue master",
         "iris",
-        "red",
-        "baseball"
+        "yellow",
+        "swimming"
       ],
       [
         "2",
-        "Carol",
-        "oneplus 9",
-        "blue master",
-        "carnations",
-        "green",
-        "soccer"
-      ],
-      [
-        "3",
-        "Eric",
-        "xiaomi mi 11",
-        "blends",
-        "roses",
-        "yellow",
-        "tennis"
-      ],
-      [
-        "4",
         "Peter",
         "iphone 13",
         "dunhill",
@@ -1677,11 +1613,29 @@
         "volleyball"
       ],
       [
+        "3",
+        "Carol",
+        "xiaomi mi 11",
+        "prince",
+        "carnations",
+        "green",
+        "soccer"
+      ],
+      [
+        "4",
+        "Eric",
+        "oneplus 9",
+        "blends",
+        "tulips",
+        "red",
+        "tennis"
+      ],
+      [
         "5",
         "Arnold",
         "huawei p50",
-        "prince",
-        "daffodils",
+        "yellow monster",
+        "roses",
         "purple",
         "basketball"
       ],
@@ -1690,8 +1644,7 @@
         "Bob",
         "google pixel 6",
         "pall mall",
-        "tulips",
-        "w</t>
+        "daffodils</t>
         </is>
       </c>
     </row>
@@ -1720,12 +1673,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>{
-  "solution": {
-    "header": [],
-    "rows": []
-  }
-}</t>
+          <t>{"solution": {"header": [], "rows": []}}</t>
         </is>
       </c>
     </row>
@@ -1743,14 +1691,14 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F6" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1758,40 +1706,40 @@
   "solution": {
     "header": [
       "House",
-      "name",
-      "child",
-      "smoothie"
+      "Name",
+      "Children",
+      "Smoothie"
     ],
     "rows": [
       [
         "1",
-        "Eric",
+        "Arnold",
         "Bella",
         "blueberry"
       ],
       [
         "2",
-        "Arnold",
-        "Timothy",
-        "lime"
-      ],
-      [
-        "3",
         "Carol",
         "Fred",
+        "cherry"
+      ],
+      [
+        "3",
+        "Eric",
+        "Samantha",
         "desert"
       ],
       [
         "4",
-        "Bob",
-        "Samantha",
-        "cherry"
-      ],
-      [
-        "5",
         "Alice",
         "Alice",
         "watermelon"
+      ],
+      [
+        "5",
+        "Bob",
+        "Timothy",
+        "lime"
       ],
       [
         "6",
@@ -1830,36 +1778,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "hobby",
-      "favorite book genre",
-      "favorite music genre",
-      "birthday month"
-    ],
-    "rows": [
-      [
-        "1",
-        "Eric",
-        "gardening",
-        "mystery",
-        "rock",
-        "sept"
-      ],
-      [
-        "2",
-        "Arnold",
-        "photography",
-        "science fiction",
-        "pop",
-        "april"
-      ]
-    ]
-  }
-}</t>
+          <t>{"solution": {}}</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1800,7 @@
         </is>
       </c>
       <c r="E8" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F8" t="b">
         <v>1</v>
@@ -1897,7 +1816,7 @@
       "Height",
       "Mother",
       "Occupation",
-      "Sport"
+      "FavoriteSport"
     ],
     "rows": [
       [
@@ -1960,7 +1879,7 @@
         </is>
       </c>
       <c r="E9" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F9" t="b">
         <v>1</v>
@@ -1972,7 +1891,7 @@
     "header": [
       "House",
       "Name",
-      "height"
+      "Height"
     ],
     "rows": [
       [
@@ -2021,67 +1940,57 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>{"solution": {"header": ["House", "Name", "Pet", "House style", "Birthday month"], "rows": [["1", "Bob", "cat", "mediterranean", "feb"], ["2", "Peter", "rabbit", "colonial", "may"], ["3", "Carol", "bird", "victorian", "mar"], ["4", "Arnold", "dog", "craftsman", "jan"], ["5", "Alice", "fish", "modern", "april"], ["6", "Eric", "hamster", "ranch", "sept"]]}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x2-27</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C11" t="b">
-        <v>0</v>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E11" t="b">
-        <v>0</v>
-      </c>
-      <c r="F11" t="b">
-        <v>1</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "height"
+      "Pet",
+      "HouseStyle",
+      "Birthday"
     ],
     "rows": [
       [
         "1",
-        "Eric",
-        "very tall"
+        "Bob",
+        "cat",
+        "mediterranean",
+        "feb"
       ],
       [
         "2",
         "Peter",
-        "short"
+        "fish",
+        "colonial",
+        "may"
       ],
       [
         "3",
-        "Bob",
-        "very short"
+        "Carol",
+        "bird",
+        "victorian",
+        "mar"
       ],
       [
         "4",
+        "Arnold",
+        "dog",
+        "craftsman",
+        "jan"
+      ],
+      [
+        "5",
         "Alice",
-        "tall"
-      ],
-      [
-        "5",
-        "Arnold",
-        "average"
+        "rabbit",
+        "modern",
+        "april"
+      ],
+      [
+        "6",
+        "Eric",
+        "hamster",
+        "ranch",
+        "sept"
       ]
     ]
   }
@@ -2089,6 +1998,35 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x2-27</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
+      </c>
+      <c r="F11" t="b">
+        <v>1</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Height"], "rows": [["1", "Eric", "very tall"], ["2", "Peter", "short"], ["3", "Bob", "very short"], ["4", "Alice", "tall"], ["5", "Arnold", "average"]]}}</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
@@ -2107,51 +2045,98 @@
         </is>
       </c>
       <c r="E12" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12" t="b">
         <v>1</v>
       </c>
       <c r="G12" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Flower", "Animal"], "rows": [["1", "Arnold", "lilies", "bird"], ["2", "Alice", "carnations", "dog"], ["3", "Eric", "tulips", "horse"], ["4", "Peter", "daffodils", "fish"], ["5", "Bob", "roses", "cat"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x6-6</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>1</v>
+      </c>
+      <c r="C13" t="b">
+        <v>0</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E13" t="b">
+        <v>0</v>
+      </c>
+      <c r="F13" t="b">
+        <v>0</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "flower",
-      "animal"
+      "Vacation",
+      "Education",
+      "Color",
+      "PhoneModel",
+      "Food"
     ],
     "rows": [
       [
         "1",
-        "Arnold",
-        "lilies",
-        "bird"
+        "Bob",
+        "camping",
+        "high school",
+        "white",
+        "iphone 13",
+        "stew"
       ],
       [
         "2",
-        "Alice",
-        "carnations",
-        "dog"
+        "Peter",
+        "mountain",
+        "bachelor",
+        "blue",
+        "huawei p50",
+        "stir fry"
       ],
       [
         "3",
         "Eric",
-        "tulips",
-        "horse"
+        "city",
+        "doctorate",
+        "yellow",
+        "samsung galaxy s21",
+        "pizza"
       ],
       [
         "4",
-        "Peter",
-        "daffodils",
-        "fish"
+        "Alice",
+        "cruise",
+        "master",
+        "green",
+        "oneplus 9",
+        "spaghetti"
       ],
       [
         "5",
-        "Bob",
-        "roses",
-        "cat"
+        "Arnold",
+        "beach",
+        "associate",
+        "red",
+        "google pixel 6",
+        "grilled cheese"
       ]
     ]
   }
@@ -2159,37 +2144,6 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x6-6</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1</v>
-      </c>
-      <c r="C13" t="b">
-        <v>1</v>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E13" t="b">
-        <v>0</v>
-      </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 21:50:16.py", line 351
-    if possibilities[i]['House'] == '2':
-IndentationError: expected an indented block after 'if' statement on line 351</t>
-        </is>
-      </c>
-    </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
@@ -2204,14 +2158,14 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Correct</t>
+          <t>Wrong plan</t>
         </is>
       </c>
       <c r="E14" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F14" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -2223,7 +2177,7 @@
       "Smoothie",
       "Cigar",
       "Height",
-      "Phone"
+      "PhoneModel"
     ],
     "rows": [
       [
@@ -2282,7 +2236,7 @@
         </is>
       </c>
       <c r="E15" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F15" t="b">
         <v>1</v>
@@ -2294,7 +2248,7 @@
     "header": [
       "House",
       "Name",
-      "style"
+      "HouseStyle"
     ],
     "rows": [
       [
@@ -2337,14 +2291,14 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F16" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -2353,8 +2307,8 @@
     "header": [
       "House",
       "Name",
-      "book genres",
-      "type of vacation"
+      "BookGenre",
+      "Vacation"
     ],
     "rows": [
       [
@@ -2384,117 +2338,123 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-6x5-8</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>1</v>
+      </c>
+      <c r="C17" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E17" t="b">
+        <v>0</v>
+      </c>
+      <c r="F17" t="b">
+        <v>0</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 00:19:32.py", line 324
+    assignments[1]['Favorite
+                   ^
+SyntaxError: unterminated string literal (detected at line 324)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-5x5-39</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>1</v>
-      </c>
-      <c r="C17" t="b">
-        <v>1</v>
-      </c>
-      <c r="D17" t="inlineStr">
+      <c r="B18" t="n">
+        <v>1</v>
+      </c>
+      <c r="C18" t="b">
+        <v>1</v>
+      </c>
+      <c r="D18" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="E17" t="b">
-        <v>0</v>
-      </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
-      <c r="G17" t="inlineStr">
+      <c r="E18" t="b">
+        <v>0</v>
+      </c>
+      <c r="F18" t="b">
+        <v>0</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:47:39.py", line 177, in &lt;module&gt;
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-14 22:19:16.py", line 169, in &lt;module&gt;
     print(solve_puzzle())
           ^^^^^^^^^^^^^^
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:47:39.py", line 30, in solve_puzzle
-    for i in range(5):
-             ^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-14 22:19:16.py", line 39, in solve_puzzle
+    assignment.append(house)
 KeyboardInterrupt</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x2-10</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C18" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E18" t="b">
-        <v>1</v>
-      </c>
-      <c r="F18" t="b">
-        <v>1</v>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "Height"
-    ],
-    "rows": [
-      [
-        "1",
-        "Peter",
-        "average"
-      ],
-      [
-        "2",
-        "Eric",
-        "very short"
-      ],
-      [
-        "3",
-        "Arnold",
-        "short"
-      ]
-    ]
-  }
-}</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-3x2-10</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>1</v>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19" t="b">
+        <v>1</v>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Height"], "rows": [["1", "Peter", "average"], ["2", "Eric", "very short"], ["3", "Arnold", "short"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-5x3-35</t>
         </is>
       </c>
-      <c r="B19" t="n">
-        <v>1</v>
-      </c>
-      <c r="C19" t="b">
-        <v>0</v>
-      </c>
-      <c r="D19" t="inlineStr">
+      <c r="B20" t="n">
+        <v>1</v>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E19" t="b">
-        <v>1</v>
-      </c>
-      <c r="F19" t="b">
-        <v>1</v>
-      </c>
-      <c r="G19" t="inlineStr">
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20" t="b">
+        <v>1</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -2541,37 +2501,37 @@
         </is>
       </c>
     </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+    <row r="21">
+      <c r="A21" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-4x2-32</t>
         </is>
       </c>
-      <c r="B20" t="n">
-        <v>1</v>
-      </c>
-      <c r="C20" t="b">
-        <v>0</v>
-      </c>
-      <c r="D20" t="inlineStr">
+      <c r="B21" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E20" t="b">
-        <v>0</v>
-      </c>
-      <c r="F20" t="b">
-        <v>1</v>
-      </c>
-      <c r="G20" t="inlineStr">
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21" t="b">
+        <v>1</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "pet"
+      "Pet"
     ],
     "rows": [
       [
@@ -2600,37 +2560,37 @@
         </is>
       </c>
     </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+    <row r="22">
+      <c r="A22" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-4x2-28</t>
         </is>
       </c>
-      <c r="B21" t="n">
-        <v>1</v>
-      </c>
-      <c r="C21" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" t="inlineStr">
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="b">
+        <v>0</v>
+      </c>
+      <c r="D22" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E21" t="b">
-        <v>0</v>
-      </c>
-      <c r="F21" t="b">
-        <v>1</v>
-      </c>
-      <c r="G21" t="inlineStr">
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22" t="b">
+        <v>1</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "hair"
+      "HairColor"
     ],
     "rows": [
       [
@@ -2659,133 +2619,69 @@
         </is>
       </c>
     </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x6-29</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>1</v>
-      </c>
-      <c r="C22" t="b">
-        <v>1</v>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E22" t="b">
-        <v>0</v>
-      </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 21:50:16.py", line 71
-    else:
-    ^^^^
-SyntaxError: invalid syntax</t>
-        </is>
-      </c>
-    </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-3x6-31</t>
+          <t>zebralogic_example_lgp-test-3x6-29</t>
         </is>
       </c>
       <c r="B23" t="n">
         <v>1</v>
       </c>
       <c r="C23" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G23" t="inlineStr">
-        <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 21:50:16.py", line 85
-    else:
-    ^^^^
-SyntaxError: invalid syntax</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x6-16</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1</v>
-      </c>
-      <c r="C24" t="b">
-        <v>0</v>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E24" t="b">
-        <v>0</v>
-      </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
-      <c r="G24" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
+      "Animal",
+      "Birthday",
+      "Hobby",
       "Drink",
-      "Nationality",
-      "Education",
-      "House Style",
-      "Smoothie"
+      "HairColor"
     ],
     "rows": [
       [
         "1",
+        "Peter",
+        "horse",
+        "jan",
+        "photography",
+        "water",
+        "blonde"
+      ],
+      [
+        "2",
         "Eric",
-        "milk",
-        "dane",
-        "high school",
-        "ranch",
-        "watermelon"
-      ],
-      [
-        "2",
-        "Peter",
-        "water",
-        "swede",
-        "bachelor",
-        "victorian",
-        "desert"
+        "cat",
+        "sept",
+        "cooking",
+        "tea",
+        "brown"
       ],
       [
         "3",
         "Arnold",
-        "tea",
-        "brit",
-        "associate",
-        "colonial",
-        "cherry"
+        "bird",
+        "april",
+        "gardening",
+        "milk",
+        "black"
       ]
     ]
   }
@@ -2793,21 +2689,53 @@
         </is>
       </c>
     </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x6-31</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" t="b">
+        <v>1</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E24" t="b">
+        <v>0</v>
+      </c>
+      <c r="F24" t="b">
+        <v>0</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-14 21:41:45.py", line 98
+    else:
+    ^^^^
+SyntaxError: invalid syntax</t>
+        </is>
+      </c>
+    </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-6x3-13</t>
+          <t>zebralogic_example_lgp-test-3x6-16</t>
         </is>
       </c>
       <c r="B25" t="n">
         <v>1</v>
       </c>
       <c r="C25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Wrong plan</t>
         </is>
       </c>
       <c r="E25" t="b">
@@ -2818,17 +2746,14 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:30:46.py", line 159
-    remaining_occupation = [o for o in occupations if o not in [h['occupation'] for h in current_houses_artist if h['occupation'] is not None][0]
-                           ^
-SyntaxError: '[' was never closed</t>
+          <t>{"solution": {"header": [], "rows": []}}</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-3x6-9</t>
+          <t>zebralogic_example_lgp-test-6x3-13</t>
         </is>
       </c>
       <c r="B26" t="n">
@@ -2839,14 +2764,14 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F26" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -2855,39 +2780,45 @@
     "header": [
       "House",
       "Name",
-      "car",
-      "house",
-      "pet",
-      "occupation",
-      "vacation"
+      "BookGenre",
+      "Occupation"
     ],
     "rows": [
       [
         "1",
+        "Carol",
+        "mystery",
+        "doctor"
+      ],
+      [
+        "2",
+        "Bob",
+        "science fiction",
+        "artist"
+      ],
+      [
+        "3",
+        "Eric",
+        "historical fiction",
+        "nurse"
+      ],
+      [
+        "4",
+        "Alice",
+        "fantasy",
+        "lawyer"
+      ],
+      [
+        "5",
         "Arnold",
-        "tesla model 3",
-        "ranch",
-        "fish",
-        "doctor",
-        "city"
-      ],
-      [
-        "2",
-        "Eric",
-        "toyota camry",
-        "victorian",
-        "dog",
-        "engineer",
-        "beach"
-      ],
-      [
-        "3",
+        "biography",
+        "teacher"
+      ],
+      [
+        "6",
         "Peter",
-        "ford f150",
-        "colonial",
-        "cat",
-        "teacher",
-        "mountain"
+        "romance",
+        "engineer"
       ]
     ]
   }
@@ -2898,27 +2829,59 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-3x6-9</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E27" t="b">
+        <v>0</v>
+      </c>
+      <c r="F27" t="b">
+        <v>0</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-14 21:41:45.py", line 96
+    else:
+    ^^^^
+SyntaxError: invalid syntax</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-3x6-35</t>
         </is>
       </c>
-      <c r="B27" t="n">
-        <v>1</v>
-      </c>
-      <c r="C27" t="b">
-        <v>0</v>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E27" t="b">
-        <v>0</v>
-      </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
-      <c r="G27" t="inlineStr">
+      <c r="B28" t="n">
+        <v>1</v>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
+      </c>
+      <c r="F28" t="b">
+        <v>1</v>
+      </c>
+      <c r="G28" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -2928,7 +2891,7 @@
       "Vacation",
       "Height",
       "Flower",
-      "Hair Color",
+      "HairColor",
       "Education"
     ],
     "rows": [
@@ -2965,38 +2928,38 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
+    <row r="29">
+      <c r="A29" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-3x3-0</t>
         </is>
       </c>
-      <c r="B28" t="n">
-        <v>1</v>
-      </c>
-      <c r="C28" t="b">
-        <v>0</v>
-      </c>
-      <c r="D28" t="inlineStr">
+      <c r="B29" t="n">
+        <v>1</v>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E28" t="b">
-        <v>0</v>
-      </c>
-      <c r="F28" t="b">
-        <v>1</v>
-      </c>
-      <c r="G28" t="inlineStr">
+      <c r="E29" t="b">
+        <v>1</v>
+      </c>
+      <c r="F29" t="b">
+        <v>1</v>
+      </c>
+      <c r="G29" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "education",
-      "occupation"
+      "Education",
+      "Occupation"
     ],
     "rows": [
       [
@@ -3023,78 +2986,46 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
+    <row r="30">
+      <c r="A30" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-5x6-8</t>
         </is>
       </c>
-      <c r="B29" t="n">
-        <v>1</v>
-      </c>
-      <c r="C29" t="b">
-        <v>1</v>
-      </c>
-      <c r="D29" t="inlineStr">
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="E29" t="b">
-        <v>0</v>
-      </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
-      <c r="G29" t="inlineStr">
+      <c r="E30" t="b">
+        <v>0</v>
+      </c>
+      <c r="F30" t="b">
+        <v>0</v>
+      </c>
+      <c r="G30" t="inlineStr">
         <is>
           <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 21:50:16.py", line 252, in &lt;module&gt;
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:57:19.py", line 213, in &lt;module&gt;
     print(solve_puzzle())
           ^^^^^^^^^^^^^^
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 21:50:16.py", line 240, in solve_puzzle
-    solution[i]['name'],
-    ~~~~~~~~~~~^^^^^^^^
-KeyError: 'name'</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x4-32</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" t="b">
-        <v>1</v>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E30" t="b">
-        <v>0</v>
-      </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:30:46.py", line 395
-    ["6", "
-          ^
-SyntaxError: unterminated string literal (detected at line 395)</t>
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:57:19.py", line 85, in solve_puzzle
+    elif solution[house]['Animal'] == 'cat' and solution[house]['Drink'] != 'root beer':
+                                                ^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^^
+KeyboardInterrupt</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x6-5</t>
+          <t>zebralogic_example_lgp-test-6x4-32</t>
         </is>
       </c>
       <c r="B31" t="n">
@@ -3121,11 +3052,94 @@
     "header": [
       "House",
       "Name",
-      "occupation",
-      "birthday month",
-      "house style",
-      "height",
-      "cigar"
+      "HouseStyle",
+      "MusicGenre",
+      "Hobby"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "craftsman",
+        "country",
+        "painting"
+      ],
+      [
+        "2",
+        "Carol",
+        "mediterranean",
+        "hip hop",
+        "cooking"
+      ],
+      [
+        "3",
+        "Bob",
+        "colonial",
+        "classical",
+        "knitting"
+      ],
+      [
+        "4",
+        "Alice",
+        "victorian",
+        "jazz",
+        "photography"
+      ],
+      [
+        "5",
+        "Eric",
+        "ranch",
+        "rock",
+        "gardening"
+      ],
+      [
+        "6",
+        "Peter",
+        "modern",
+        "pop",
+        "woodworking"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x6-5</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
+      </c>
+      <c r="F32" t="b">
+        <v>1</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Occupation",
+      "Birthday",
+      "HouseStyle",
+      "Height",
+      "Cigar"
     ],
     "rows": [
       [
@@ -3152,62 +3166,88 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x5-23</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1</v>
-      </c>
-      <c r="C32" t="b">
-        <v>1</v>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E32" t="b">
-        <v>0</v>
-      </c>
-      <c r="F32" t="b">
-        <v>0</v>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 21:50:16.py", line 72
-    }
-    ^
-SyntaxError: closing parenthesis '}' does not match opening parenthesis '[' on line 69</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-2x5-23</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C33" t="b">
+        <v>0</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E33" t="b">
+        <v>0</v>
+      </c>
+      <c r="F33" t="b">
+        <v>0</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Education",
+      "Height",
+      "Food",
+      "Drink"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "associate",
+        "short",
+        "pizza",
+        "tea"
+      ],
+      [
+        "2",
+        "Eric",
+        "high school",
+        "very short",
+        "grilled cheese",
+        "water"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-2x4-11</t>
         </is>
       </c>
-      <c r="B33" t="n">
-        <v>1</v>
-      </c>
-      <c r="C33" t="b">
-        <v>0</v>
-      </c>
-      <c r="D33" t="inlineStr">
+      <c r="B34" t="n">
+        <v>1</v>
+      </c>
+      <c r="C34" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E33" t="b">
-        <v>1</v>
-      </c>
-      <c r="F33" t="b">
-        <v>1</v>
-      </c>
-      <c r="G33" t="inlineStr">
+      <c r="E34" t="b">
+        <v>1</v>
+      </c>
+      <c r="F34" t="b">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -3239,39 +3279,10 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x5-3</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1</v>
-      </c>
-      <c r="C34" t="b">
-        <v>0</v>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E34" t="b">
-        <v>0</v>
-      </c>
-      <c r="F34" t="b">
-        <v>0</v>
-      </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": [], "rows": []}}</t>
-        </is>
-      </c>
-    </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x4-30</t>
+          <t>zebralogic_example_lgp-test-3x5-3</t>
         </is>
       </c>
       <c r="B35" t="n">
@@ -3293,34 +3304,126 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>{"solution": {}}</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Smoothie",
+      "Flower",
+      "Animal",
+      "Hobby"
+    ],
+    "rows": [
+      [
+        "1",
+        "Eric",
+        "cherry",
+        "carnations",
+        "cat",
+        "photography"
+      ],
+      [
+        "2",
+        "Arnold",
+        "desert",
+        "lilies",
+        "horse",
+        "cooking"
+      ],
+      [
+        "3",
+        "Peter",
+        "watermelon",
+        "daffodils",
+        "bird",
+        "gardening"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-2x4-30</t>
+        </is>
+      </c>
+      <c r="B36" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" t="b">
+        <v>0</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
+      </c>
+      <c r="F36" t="b">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "HairColor",
+      "FavoriteSport",
+      "Smoothie"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "brown",
+        "basketball",
+        "desert"
+      ],
+      [
+        "2",
+        "Eric",
+        "black",
+        "soccer",
+        "cherry"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-4x2-8</t>
         </is>
       </c>
-      <c r="B36" t="n">
-        <v>1</v>
-      </c>
-      <c r="C36" t="b">
-        <v>0</v>
-      </c>
-      <c r="D36" t="inlineStr">
+      <c r="B37" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" t="b">
+        <v>0</v>
+      </c>
+      <c r="D37" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E36" t="b">
-        <v>1</v>
-      </c>
-      <c r="F36" t="b">
-        <v>1</v>
-      </c>
-      <c r="G36" t="inlineStr">
+      <c r="E37" t="b">
+        <v>1</v>
+      </c>
+      <c r="F37" t="b">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -3356,37 +3459,37 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-6x2-10</t>
         </is>
       </c>
-      <c r="B37" t="n">
-        <v>1</v>
-      </c>
-      <c r="C37" t="b">
-        <v>0</v>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E37" t="b">
-        <v>0</v>
-      </c>
-      <c r="F37" t="b">
-        <v>0</v>
-      </c>
-      <c r="G37" t="inlineStr">
+      <c r="B38" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" t="b">
+        <v>0</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
+      </c>
+      <c r="F38" t="b">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Music genre"
+      "MusicGenre"
     ],
     "rows": [
       [
@@ -3425,38 +3528,38 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
+    <row r="39">
+      <c r="A39" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-4x3-8</t>
         </is>
       </c>
-      <c r="B38" t="n">
-        <v>1</v>
-      </c>
-      <c r="C38" t="b">
-        <v>0</v>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E38" t="b">
-        <v>0</v>
-      </c>
-      <c r="F38" t="b">
-        <v>0</v>
-      </c>
-      <c r="G38" t="inlineStr">
+      <c r="B39" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" t="b">
+        <v>0</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
+      </c>
+      <c r="F39" t="b">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Hair Color",
-      "Music Genre"
+      "HairColor",
+      "MusicGenre"
     ],
     "rows": [
       [
@@ -3489,39 +3592,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="40">
+      <c r="A40" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-3x4-22</t>
         </is>
       </c>
-      <c r="B39" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" t="b">
-        <v>0</v>
-      </c>
-      <c r="D39" t="inlineStr">
+      <c r="B40" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" t="b">
+        <v>0</v>
+      </c>
+      <c r="D40" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E39" t="b">
-        <v>0</v>
-      </c>
-      <c r="F39" t="b">
-        <v>1</v>
-      </c>
-      <c r="G39" t="inlineStr">
+      <c r="E40" t="b">
+        <v>1</v>
+      </c>
+      <c r="F40" t="b">
+        <v>1</v>
+      </c>
+      <c r="G40" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Music",
-      "Child",
-      "Book"
+      "MusicGenre",
+      "Children",
+      "BookGenre"
     ],
     "rows": [
       [
@@ -3551,101 +3654,148 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
+    <row r="41">
+      <c r="A41" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-5x5-29</t>
         </is>
       </c>
-      <c r="B40" t="n">
-        <v>1</v>
-      </c>
-      <c r="C40" t="b">
-        <v>1</v>
-      </c>
-      <c r="D40" t="inlineStr">
+      <c r="B41" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" t="b">
+        <v>1</v>
+      </c>
+      <c r="D41" t="inlineStr">
         <is>
           <t>Error</t>
         </is>
       </c>
-      <c r="E40" t="b">
-        <v>0</v>
-      </c>
-      <c r="F40" t="b">
-        <v>0</v>
-      </c>
-      <c r="G40" t="inlineStr">
+      <c r="E41" t="b">
+        <v>0</v>
+      </c>
+      <c r="F41" t="b">
+        <v>0</v>
+      </c>
+      <c r="G41" t="inlineStr">
         <is>
           <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:16:29.py", line 207, in &lt;module&gt;
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:31:53.py", line 207, in &lt;module&gt;
     print(solve_puzzle())
           ^^^^^^^^^^^^^^
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:16:29.py", line 46, in solve_puzzle
-    continue
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:31:53.py", line 31, in solve_puzzle
+    solution.append(house)
 KeyboardInterrupt</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x4-9</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>1</v>
-      </c>
-      <c r="C41" t="b">
-        <v>1</v>
-      </c>
-      <c r="D41" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E41" t="b">
-        <v>0</v>
-      </c>
-      <c r="F41" t="b">
-        <v>0</v>
-      </c>
-      <c r="G41" t="inlineStr">
-        <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:30:46.py", line 263, in &lt;module&gt;
-    print(solve_puzzle())
-          ^^^^^^^^^^^^^^
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:30:46.py", line 250, in solve_puzzle
-    nationality = possibilities[i]['nationality'][0]
-                  ~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~~^^^
-IndexError: list index out of range</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-6x4-9</t>
+        </is>
+      </c>
+      <c r="B42" t="n">
+        <v>1</v>
+      </c>
+      <c r="C42" t="b">
+        <v>0</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
+      </c>
+      <c r="F42" t="b">
+        <v>1</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "PhoneModel",
+      "Nationality",
+      "Color"
+    ],
+    "rows": [
+      [
+        "1",
+        "Carol",
+        "xiaomi mi 11",
+        "chinese",
+        "green"
+      ],
+      [
+        "2",
+        "Arnold",
+        "oneplus 9",
+        "norwegian",
+        "purple"
+      ],
+      [
+        "3",
+        "Alice",
+        "google pixel 6",
+        "german",
+        "red"
+      ],
+      [
+        "4",
+        "Eric",
+        "huawei p50",
+        "dane",
+        "yellow"
+      ],
+      [
+        "5",
+        "Bob",
+        "samsung galaxy s21",
+        "swede",
+        "white"
+      ],
+      [
+        "6",
+        "Peter",
+        "iphone 13",
+        "brit",
+        "blue"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-3x5-19</t>
         </is>
       </c>
-      <c r="B42" t="n">
-        <v>1</v>
-      </c>
-      <c r="C42" t="b">
-        <v>0</v>
-      </c>
-      <c r="D42" t="inlineStr">
+      <c r="B43" t="n">
+        <v>1</v>
+      </c>
+      <c r="C43" t="b">
+        <v>0</v>
+      </c>
+      <c r="D43" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E42" t="b">
-        <v>1</v>
-      </c>
-      <c r="F42" t="b">
-        <v>1</v>
-      </c>
-      <c r="G42" t="inlineStr">
+      <c r="E43" t="b">
+        <v>1</v>
+      </c>
+      <c r="F43" t="b">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -3688,40 +3838,40 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
+    <row r="44">
+      <c r="A44" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-4x5-32</t>
         </is>
       </c>
-      <c r="B43" t="n">
-        <v>1</v>
-      </c>
-      <c r="C43" t="b">
-        <v>0</v>
-      </c>
-      <c r="D43" t="inlineStr">
+      <c r="B44" t="n">
+        <v>1</v>
+      </c>
+      <c r="C44" t="b">
+        <v>0</v>
+      </c>
+      <c r="D44" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E43" t="b">
-        <v>0</v>
-      </c>
-      <c r="F43" t="b">
-        <v>1</v>
-      </c>
-      <c r="G43" t="inlineStr">
+      <c r="E44" t="b">
+        <v>1</v>
+      </c>
+      <c r="F44" t="b">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "hobby",
-      "birthday month",
-      "education",
-      "smoothie"
+      "Hobby",
+      "Birthday",
+      "Education",
+      "Smoothie"
     ],
     "rows": [
       [
@@ -3762,45 +3912,10 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x3-11</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>1</v>
-      </c>
-      <c r="C44" t="b">
-        <v>1</v>
-      </c>
-      <c r="D44" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E44" t="b">
-        <v>0</v>
-      </c>
-      <c r="F44" t="b">
-        <v>0</v>
-      </c>
-      <c r="G44" t="inlineStr">
-        <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:42:43.py", line 155, in &lt;module&gt;
-    print(json.dumps(solve_puzzle(), indent=2))
-                     ^^^^^^^^^^^^^^
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:42:43.py", line 20, in solve_puzzle
-    from constraint import Problem, AllDifferentConstraint
-ModuleNotFoundError: No module named 'constraint'</t>
-        </is>
-      </c>
-    </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-4x6-21</t>
+          <t>zebralogic_example_lgp-test-6x3-11</t>
         </is>
       </c>
       <c r="B45" t="n">
@@ -3815,7 +3930,7 @@
         </is>
       </c>
       <c r="E45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F45" t="b">
         <v>0</v>
@@ -3827,48 +3942,45 @@
     "header": [
       "House",
       "Name",
-      "Flower",
-      "Hobby",
-      "Pet",
-      "Color",
-      "House Style"
+      "HairColor",
+      "Height"
     ],
     "rows": [
       [
         "1",
+        "Carol",
+        "blonde",
+        "very tall"
+      ],
+      [
+        "2",
+        "Bob",
+        "brown",
+        "average"
+      ],
+      [
+        "3",
+        "Arnold",
+        "gray",
+        "short"
+      ],
+      [
+        "4",
+        "Alice",
+        "auburn",
+        "super tall"
+      ],
+      [
+        "5",
+        "Eric",
+        "red",
+        "very short"
+      ],
+      [
+        "6",
         "Peter",
-        "daffodils",
-        "gardening",
-        "bird",
-        "yellow",
-        "ranch"
-      ],
-      [
-        "2",
-        "Arnold",
-        "carnations",
-        "painting",
-        "fish",
-        "white",
-        "craftsman"
-      ],
-      [
-        "3",
-        "Alice",
-        "roses",
-        "photography",
-        "dog",
-        "red",
-        "colonial"
-      ],
-      [
-        "4",
-        "Eric",
-        "lilies",
-        "cooking",
-        "cat",
-        "green",
-        "victorian"
+        "black",
+        "tall"
       ]
     ]
   }
@@ -3879,51 +3991,94 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-4x6-21</t>
+        </is>
+      </c>
+      <c r="B46" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" t="b">
+        <v>0</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E46" t="b">
+        <v>0</v>
+      </c>
+      <c r="F46" t="b">
+        <v>0</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [],
+    "rows": []
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-5x6-13</t>
         </is>
       </c>
-      <c r="B46" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" t="b">
-        <v>0</v>
-      </c>
-      <c r="D46" t="inlineStr">
+      <c r="B47" t="n">
+        <v>1</v>
+      </c>
+      <c r="C47" t="b">
+        <v>0</v>
+      </c>
+      <c r="D47" t="inlineStr">
         <is>
           <t>Wrong plan</t>
         </is>
       </c>
-      <c r="E46" t="b">
-        <v>0</v>
-      </c>
-      <c r="F46" t="b">
-        <v>0</v>
-      </c>
-      <c r="G46" t="inlineStr">
+      <c r="E47" t="b">
+        <v>1</v>
+      </c>
+      <c r="F47" t="b">
+        <v>0</v>
+      </c>
+      <c r="G47" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Lunch",
-      "Car",
-      "Phone",
+      "Food",
+      "CarModel",
+      "PhoneModel",
       "Occupation",
       "Drink"
     ],
     "rows": [
       [
         "1",
+        "Bob",
+        "stew",
+        "bmw 3 series",
+        "iphone 13",
+        "engineer",
+        "coffee"
+      ],
+      [
+        "2",
         "Alice",
         "stir fry",
-        "bmw 3 series",
+        "honda civic",
         "samsung galaxy s21",
         "artist",
-        "water"
-      ],
-      [
-        "2",
+        "root beer"
+      ],
+      [
+        "3",
         "Arnold",
         "spaghetti",
         "toyota camry",
@@ -3932,19 +4087,10 @@
         "tea"
       ],
       [
-        "3",
-        "Bob",
-        "stew",
-        "ford f150",
-        "iphone 13",
-        "engineer",
-        "coffee"
-      ],
-      [
         "4",
         "Eric",
         "pizza",
-        "tesla model 3",
+        "ford f150",
         "oneplus 9",
         "lawyer",
         "milk"
@@ -3953,10 +4099,10 @@
         "5",
         "Peter",
         "grilled cheese",
-        "honda civic",
+        "tesla model 3",
         "huawei p50",
         "teacher",
-        "root beer"
+        "water"
       ]
     ]
   }
@@ -3964,62 +4110,62 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x4-14</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>1</v>
-      </c>
-      <c r="C47" t="b">
-        <v>1</v>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E47" t="b">
-        <v>0</v>
-      </c>
-      <c r="F47" t="b">
-        <v>0</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 22:16:29.py", line 55
-    h['name'] = [n for n in h['name'] if n != 'Carol'  # Wait, this doesn't make sense
-                ^
-SyntaxError: '[' was never closed</t>
-        </is>
-      </c>
-    </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-6x4-14</t>
+        </is>
+      </c>
+      <c r="B48" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" t="b">
+        <v>1</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E48" t="b">
+        <v>0</v>
+      </c>
+      <c r="F48" t="b">
+        <v>0</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 00:19:32.py", line 289
+    assignments[5
+               ^
+SyntaxError: '[' was never closed</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-6x3-27</t>
         </is>
       </c>
-      <c r="B48" t="n">
-        <v>1</v>
-      </c>
-      <c r="C48" t="b">
-        <v>0</v>
-      </c>
-      <c r="D48" t="inlineStr">
+      <c r="B49" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" t="b">
+        <v>0</v>
+      </c>
+      <c r="D49" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E48" t="b">
-        <v>0</v>
-      </c>
-      <c r="F48" t="b">
-        <v>1</v>
-      </c>
-      <c r="G48" t="inlineStr">
+      <c r="E49" t="b">
+        <v>1</v>
+      </c>
+      <c r="F49" t="b">
+        <v>1</v>
+      </c>
+      <c r="G49" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -4027,7 +4173,7 @@
       "House",
       "Name",
       "Occupation",
-      "Car"
+      "CarModel"
     ],
     "rows": [
       [
@@ -4072,37 +4218,37 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
+    <row r="50">
+      <c r="A50" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-6x2-4</t>
         </is>
       </c>
-      <c r="B49" t="n">
-        <v>1</v>
-      </c>
-      <c r="C49" t="b">
-        <v>0</v>
-      </c>
-      <c r="D49" t="inlineStr">
+      <c r="B50" t="n">
+        <v>1</v>
+      </c>
+      <c r="C50" t="b">
+        <v>0</v>
+      </c>
+      <c r="D50" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E49" t="b">
-        <v>0</v>
-      </c>
-      <c r="F49" t="b">
-        <v>1</v>
-      </c>
-      <c r="G49" t="inlineStr">
+      <c r="E50" t="b">
+        <v>1</v>
+      </c>
+      <c r="F50" t="b">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Phone"
+      "PhoneModel"
     ],
     "rows": [
       [
@@ -4141,78 +4287,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x5-11</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1</v>
-      </c>
-      <c r="C50" t="b">
-        <v>1</v>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>Error</t>
-        </is>
-      </c>
-      <c r="E50" t="b">
-        <v>0</v>
-      </c>
-      <c r="F50" t="b">
-        <v>0</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>Traceback (most recent call last):
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 21:50:16.py", line 235, in &lt;module&gt;
-    solution = solve_puzzle()
-               ^^^^^^^^^^^^^^
-  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 21:50:16.py", line 53, in solve_puzzle
-    if house['Name'] == 'Alice':
-       ^^^^^^^^^^^^^^^^^^^^^^^^
-KeyboardInterrupt</t>
-        </is>
-      </c>
-    </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-2x4-14</t>
+          <t>zebralogic_example_lgp-test-5x5-11</t>
         </is>
       </c>
       <c r="B51" t="n">
         <v>1</v>
       </c>
       <c r="C51" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F51" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 21:50:16.py", line 65
-    }
-    ^
-SyntaxError: closing parenthesis '}' does not match opening parenthesis '[' on line 62</t>
+          <t>{"solution": {"header": ["House", "Name", "Height", "Cigar", "Smoothie", "PhoneModel"], "rows": [["1", "Peter", "short", "blends", "watermelon", "samsung galaxy s21"], ["2", "Eric", "very tall", "prince", "desert", "iphone 13"], ["3", "Arnold", "tall", "blue master", "cherry", "oneplus 9"], ["4", "Alice", "very short", "pall mall", "lime", "huawei p50"], ["5", "Bob", "average", "dunhill", "dragonfruit", "google pixel 6"]]}}</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-5x4-2</t>
+          <t>zebralogic_example_lgp-test-2x4-14</t>
         </is>
       </c>
       <c r="B52" t="n">
@@ -4223,54 +4330,109 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Wrong plan</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F52" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G52" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": [], "rows": []}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x4-26</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1</v>
-      </c>
-      <c r="C53" t="b">
-        <v>0</v>
-      </c>
-      <c r="D53" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E53" t="b">
-        <v>0</v>
-      </c>
-      <c r="F53" t="b">
-        <v>0</v>
-      </c>
-      <c r="G53" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "height",
-      "mother",
-      "hair_color"
+      "HouseStyle",
+      "Smoothie",
+      "Pet"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "victorian",
+        "cherry",
+        "dog"
+      ],
+      [
+        "2",
+        "Eric",
+        "colonial",
+        "desert",
+        "cat"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x4-2</t>
+        </is>
+      </c>
+      <c r="B53" t="n">
+        <v>1</v>
+      </c>
+      <c r="C53" t="b">
+        <v>0</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E53" t="b">
+        <v>0</v>
+      </c>
+      <c r="F53" t="b">
+        <v>0</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": [], "rows": []}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x4-26</t>
+        </is>
+      </c>
+      <c r="B54" t="n">
+        <v>1</v>
+      </c>
+      <c r="C54" t="b">
+        <v>0</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="b">
+        <v>0</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Height",
+      "Mother",
+      "HairColor"
     ],
     "rows": [
       [
@@ -4314,37 +4476,37 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
+    <row r="55">
+      <c r="A55" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-2x2-5</t>
         </is>
       </c>
-      <c r="B54" t="n">
-        <v>1</v>
-      </c>
-      <c r="C54" t="b">
-        <v>0</v>
-      </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E54" t="b">
-        <v>0</v>
-      </c>
-      <c r="F54" t="b">
-        <v>0</v>
-      </c>
-      <c r="G54" t="inlineStr">
+      <c r="B55" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" t="b">
+        <v>0</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="b">
+        <v>1</v>
+      </c>
+      <c r="G55" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "house"
+      "HouseStyle"
     ],
     "rows": [
       [
@@ -4363,39 +4525,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
+    <row r="56">
+      <c r="A56" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-2x4-36</t>
         </is>
       </c>
-      <c r="B55" t="n">
-        <v>1</v>
-      </c>
-      <c r="C55" t="b">
-        <v>0</v>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E55" t="b">
-        <v>0</v>
-      </c>
-      <c r="F55" t="b">
-        <v>0</v>
-      </c>
-      <c r="G55" t="inlineStr">
+      <c r="B56" t="n">
+        <v>1</v>
+      </c>
+      <c r="C56" t="b">
+        <v>0</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="b">
+        <v>1</v>
+      </c>
+      <c r="G56" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "book genre",
-      "birthday month",
-      "animal"
+      "BookGenre",
+      "Birthday",
+      "Animal"
     ],
     "rows": [
       [
@@ -4418,37 +4580,37 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
+    <row r="57">
+      <c r="A57" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-5x4-27</t>
         </is>
       </c>
-      <c r="B56" t="n">
-        <v>1</v>
-      </c>
-      <c r="C56" t="b">
-        <v>0</v>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E56" t="b">
-        <v>0</v>
-      </c>
-      <c r="F56" t="b">
-        <v>0</v>
-      </c>
-      <c r="G56" t="inlineStr">
+      <c r="B57" t="n">
+        <v>1</v>
+      </c>
+      <c r="C57" t="b">
+        <v>0</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="b">
+        <v>1</v>
+      </c>
+      <c r="G57" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Month",
+      "Birthday",
       "Cigar",
       "Drink"
     ],
@@ -4465,28 +4627,28 @@
         "Alice",
         "feb",
         "blends",
-        "water"
+        "tea"
       ],
       [
         "3",
         "Eric",
         "jan",
         "pall mall",
-        "tea"
+        "root beer"
       ],
       [
         "4",
         "Arnold",
-        "mar",
-        "dunhill",
-        ""
-      ],
-      [
-        "5",
-        "Peter",
         "sept",
         "blue master",
         "coffee"
+      ],
+      [
+        "5",
+        "Peter",
+        "mar",
+        "dunhill",
+        "water"
       ]
     ]
   }
@@ -4494,30 +4656,30 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
+    <row r="58">
+      <c r="A58" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-3x3-29</t>
         </is>
       </c>
-      <c r="B57" t="n">
-        <v>1</v>
-      </c>
-      <c r="C57" t="b">
-        <v>0</v>
-      </c>
-      <c r="D57" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E57" t="b">
-        <v>0</v>
-      </c>
-      <c r="F57" t="b">
-        <v>0</v>
-      </c>
-      <c r="G57" t="inlineStr">
+      <c r="B58" t="n">
+        <v>1</v>
+      </c>
+      <c r="C58" t="b">
+        <v>0</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="b">
+        <v>1</v>
+      </c>
+      <c r="G58" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -4525,7 +4687,7 @@
       "House",
       "Name",
       "Mother",
-      "Lunch"
+      "Food"
     ],
     "rows": [
       [
@@ -4552,91 +4714,167 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x6-11</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>1</v>
-      </c>
-      <c r="C58" t="b">
-        <v>0</v>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E58" t="b">
-        <v>0</v>
-      </c>
-      <c r="F58" t="b">
-        <v>0</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": [], "rows": []}}</t>
-        </is>
-      </c>
-    </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>zebralogic_example_lgp-test-3x3-19</t>
+          <t>zebralogic_example_lgp-test-4x6-11</t>
         </is>
       </c>
       <c r="B59" t="n">
         <v>1</v>
       </c>
       <c r="C59" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Error</t>
+          <t>Correct</t>
         </is>
       </c>
       <c r="E59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-11 21:50:16.py", line 43
-    mystery_index = next(i for i, h in enumerate(assignment) if h["book genres"] == "mystery" else -1
-                                                                                              ^^^^
-SyntaxError: invalid syntax</t>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Hobby",
+      "Animal",
+      "BookGenre",
+      "Birthday",
+      "MusicGenre"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "painting",
+        "fish",
+        "fantasy",
+        "feb",
+        "pop"
+      ],
+      [
+        "2",
+        "Alice",
+        "cooking",
+        "bird",
+        "romance",
+        "sept",
+        "jazz"
+      ],
+      [
+        "3",
+        "Arnold",
+        "gardening",
+        "horse",
+        "mystery",
+        "april",
+        "rock"
+      ],
+      [
+        "4",
+        "Eric",
+        "photography",
+        "cat",
+        "science fiction",
+        "jan",
+        "classical"
+      ]
+    ]
+  }
+}</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-3x3-19</t>
+        </is>
+      </c>
+      <c r="B60" t="n">
+        <v>1</v>
+      </c>
+      <c r="C60" t="b">
+        <v>0</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="b">
+        <v>1</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [
+      "House",
+      "Name",
+      "Smoothie",
+      "BookGenre"
+    ],
+    "rows": [
+      [
+        "1",
+        "Peter",
+        "cherry",
+        "romance"
+      ],
+      [
+        "2",
+        "Eric",
+        "desert",
+        "science fiction"
+      ],
+      [
+        "3",
+        "Arnold",
+        "watermelon",
+        "mystery"
+      ]
+    ]
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-5x3-25</t>
         </is>
       </c>
-      <c r="B60" t="n">
-        <v>1</v>
-      </c>
-      <c r="C60" t="b">
-        <v>0</v>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E60" t="b">
-        <v>0</v>
-      </c>
-      <c r="F60" t="b">
-        <v>0</v>
-      </c>
-      <c r="G60" t="inlineStr">
+      <c r="B61" t="n">
+        <v>1</v>
+      </c>
+      <c r="C61" t="b">
+        <v>0</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="b">
+        <v>1</v>
+      </c>
+      <c r="G61" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -4644,7 +4882,7 @@
       "House",
       "Name",
       "Height",
-      "Lunch"
+      "Food"
     ],
     "rows": [
       [
@@ -4683,69 +4921,69 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x2-14</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>1</v>
-      </c>
-      <c r="C61" t="b">
-        <v>0</v>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E61" t="b">
-        <v>0</v>
-      </c>
-      <c r="F61" t="b">
-        <v>1</v>
-      </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": ["House", "Name", "cigar"], "rows": [["1", "Peter", "dunhill"], ["2", "Arnold", "yellow monster"], ["3", "Bob", "pall mall"], ["4", "Alice", "blends"], ["5", "Carol", "blue master"], ["6", "Eric", "prince"]]}}</t>
-        </is>
-      </c>
-    </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
+          <t>zebralogic_example_lgp-test-6x2-14</t>
+        </is>
+      </c>
+      <c r="B62" t="n">
+        <v>1</v>
+      </c>
+      <c r="C62" t="b">
+        <v>0</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" t="b">
+        <v>1</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Cigar"], "rows": [["1", "Peter", "dunhill"], ["2", "Arnold", "yellow monster"], ["3", "Bob", "pall mall"], ["4", "Alice", "blends"], ["5", "Carol", "blue master"], ["6", "Eric", "prince"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
           <t>zebralogic_example_lgp-test-4x5-14</t>
         </is>
       </c>
-      <c r="B62" t="n">
-        <v>1</v>
-      </c>
-      <c r="C62" t="b">
-        <v>0</v>
-      </c>
-      <c r="D62" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E62" t="b">
-        <v>0</v>
-      </c>
-      <c r="F62" t="b">
-        <v>1</v>
-      </c>
-      <c r="G62" t="inlineStr">
+      <c r="B63" t="n">
+        <v>1</v>
+      </c>
+      <c r="C63" t="b">
+        <v>0</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="b">
+        <v>0</v>
+      </c>
+      <c r="G63" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "mother's name",
-      "smoothie",
-      "height",
-      "education"
+      "Mother",
+      "Smoothie",
+      "Height",
+      "Education"
     ],
     "rows": [
       [
@@ -4786,171 +5024,95 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
+    <row r="64">
+      <c r="A64" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-5x2-18</t>
         </is>
       </c>
-      <c r="B63" t="n">
-        <v>1</v>
-      </c>
-      <c r="C63" t="b">
-        <v>0</v>
-      </c>
-      <c r="D63" t="inlineStr">
+      <c r="B64" t="n">
+        <v>1</v>
+      </c>
+      <c r="C64" t="b">
+        <v>0</v>
+      </c>
+      <c r="D64" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E63" t="b">
-        <v>0</v>
-      </c>
-      <c r="F63" t="b">
-        <v>1</v>
-      </c>
-      <c r="G63" t="inlineStr">
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="b">
+        <v>1</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Children"], "rows": [["1", "Bob", "Timothy"], ["2", "Alice", "Fred"], ["3", "Arnold", "Bella"], ["4", "Eric", "Samantha"], ["5", "Peter", "Meredith"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x3-22</t>
+        </is>
+      </c>
+      <c r="B65" t="n">
+        <v>1</v>
+      </c>
+      <c r="C65" t="b">
+        <v>0</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="b">
+        <v>1</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Smoothie", "Nationality"], "rows": [["1", "Arnold", "lime", "swede"], ["2", "Peter", "dragonfruit", "german"], ["3", "Alice", "watermelon", "norwegian"], ["4", "Bob", "desert", "dane"], ["5", "Eric", "cherry", "brit"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x2-2</t>
+        </is>
+      </c>
+      <c r="B66" t="n">
+        <v>1</v>
+      </c>
+      <c r="C66" t="b">
+        <v>0</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E66" t="b">
+        <v>1</v>
+      </c>
+      <c r="F66" t="b">
+        <v>1</v>
+      </c>
+      <c r="G66" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Child"
-    ],
-    "rows": [
-      [
-        "1",
-        "Bob",
-        "Timothy"
-      ],
-      [
-        "2",
-        "Alice",
-        "Fred"
-      ],
-      [
-        "3",
-        "Arnold",
-        "Bella"
-      ],
-      [
-        "4",
-        "Eric",
-        "Samantha"
-      ],
-      [
-        "5",
-        "Peter",
-        "Meredith"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x3-22</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>1</v>
-      </c>
-      <c r="C64" t="b">
-        <v>0</v>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E64" t="b">
-        <v>0</v>
-      </c>
-      <c r="F64" t="b">
-        <v>0</v>
-      </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "Smoothie",
-      "Nationality"
-    ],
-    "rows": [
-      [
-        "1",
-        "Arnold",
-        "lime",
-        "german"
-      ],
-      [
-        "2",
-        "Peter",
-        "dragonfruit",
-        "swede"
-      ],
-      [
-        "3",
-        "Alice",
-        "watermelon",
-        "norwegian"
-      ],
-      [
-        "4",
-        "Bob",
-        "desert",
-        "dane"
-      ],
-      [
-        "5",
-        "Eric",
-        "cherry",
-        "brit"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x2-2</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>1</v>
-      </c>
-      <c r="C65" t="b">
-        <v>0</v>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E65" t="b">
-        <v>0</v>
-      </c>
-      <c r="F65" t="b">
-        <v>1</v>
-      </c>
-      <c r="G65" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "style"
+      "HouseStyle"
     ],
     "rows": [
       [
@@ -4979,30 +5141,62 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x5-38</t>
+        </is>
+      </c>
+      <c r="B67" t="n">
+        <v>1</v>
+      </c>
+      <c r="C67" t="b">
+        <v>1</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E67" t="b">
+        <v>0</v>
+      </c>
+      <c r="F67" t="b">
+        <v>0</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 00:19:32.py", line 331
+    house.get('Birthday', '),
+                          ^
+SyntaxError: unterminated string literal (detected at line 331)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-6x2-5</t>
         </is>
       </c>
-      <c r="B66" t="n">
-        <v>1</v>
-      </c>
-      <c r="C66" t="b">
-        <v>0</v>
-      </c>
-      <c r="D66" t="inlineStr">
+      <c r="B68" t="n">
+        <v>1</v>
+      </c>
+      <c r="C68" t="b">
+        <v>0</v>
+      </c>
+      <c r="D68" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E66" t="b">
-        <v>1</v>
-      </c>
-      <c r="F66" t="b">
-        <v>1</v>
-      </c>
-      <c r="G66" t="inlineStr">
+      <c r="E68" t="b">
+        <v>1</v>
+      </c>
+      <c r="F68" t="b">
+        <v>1</v>
+      </c>
+      <c r="G68" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -5048,30 +5242,30 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
+    <row r="69">
+      <c r="A69" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-6x3-18</t>
         </is>
       </c>
-      <c r="B67" t="n">
-        <v>1</v>
-      </c>
-      <c r="C67" t="b">
-        <v>0</v>
-      </c>
-      <c r="D67" t="inlineStr">
+      <c r="B69" t="n">
+        <v>1</v>
+      </c>
+      <c r="C69" t="b">
+        <v>0</v>
+      </c>
+      <c r="D69" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E67" t="b">
-        <v>1</v>
-      </c>
-      <c r="F67" t="b">
-        <v>1</v>
-      </c>
-      <c r="G67" t="inlineStr">
+      <c r="E69" t="b">
+        <v>1</v>
+      </c>
+      <c r="F69" t="b">
+        <v>1</v>
+      </c>
+      <c r="G69" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -5124,40 +5318,40 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
+    <row r="70">
+      <c r="A70" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-3x5-17</t>
         </is>
       </c>
-      <c r="B68" t="n">
-        <v>1</v>
-      </c>
-      <c r="C68" t="b">
-        <v>0</v>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E68" t="b">
-        <v>0</v>
-      </c>
-      <c r="F68" t="b">
-        <v>0</v>
-      </c>
-      <c r="G68" t="inlineStr">
+      <c r="B70" t="n">
+        <v>1</v>
+      </c>
+      <c r="C70" t="b">
+        <v>0</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E70" t="b">
+        <v>1</v>
+      </c>
+      <c r="F70" t="b">
+        <v>1</v>
+      </c>
+      <c r="G70" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Phone",
+      "PhoneModel",
       "Height",
-      "House Style",
-      "Car"
+      "HouseStyle",
+      "CarModel"
     ],
     "rows": [
       [
@@ -5190,38 +5384,38 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
+    <row r="71">
+      <c r="A71" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-2x3-23</t>
         </is>
       </c>
-      <c r="B69" t="n">
-        <v>1</v>
-      </c>
-      <c r="C69" t="b">
-        <v>0</v>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E69" t="b">
-        <v>0</v>
-      </c>
-      <c r="F69" t="b">
-        <v>0</v>
-      </c>
-      <c r="G69" t="inlineStr">
+      <c r="B71" t="n">
+        <v>1</v>
+      </c>
+      <c r="C71" t="b">
+        <v>0</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E71" t="b">
+        <v>1</v>
+      </c>
+      <c r="F71" t="b">
+        <v>1</v>
+      </c>
+      <c r="G71" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Child",
-      "Lunch"
+      "Children",
+      "Food"
     ],
     "rows": [
       [
@@ -5242,30 +5436,30 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-3x3-23</t>
         </is>
       </c>
-      <c r="B70" t="n">
-        <v>1</v>
-      </c>
-      <c r="C70" t="b">
-        <v>0</v>
-      </c>
-      <c r="D70" t="inlineStr">
+      <c r="B72" t="n">
+        <v>1</v>
+      </c>
+      <c r="C72" t="b">
+        <v>0</v>
+      </c>
+      <c r="D72" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E70" t="b">
-        <v>1</v>
-      </c>
-      <c r="F70" t="b">
-        <v>1</v>
-      </c>
-      <c r="G70" t="inlineStr">
+      <c r="E72" t="b">
+        <v>1</v>
+      </c>
+      <c r="F72" t="b">
+        <v>1</v>
+      </c>
+      <c r="G72" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -5300,38 +5494,38 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
+    <row r="73">
+      <c r="A73" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-2x3-8</t>
         </is>
       </c>
-      <c r="B71" t="n">
-        <v>1</v>
-      </c>
-      <c r="C71" t="b">
-        <v>0</v>
-      </c>
-      <c r="D71" t="inlineStr">
+      <c r="B73" t="n">
+        <v>1</v>
+      </c>
+      <c r="C73" t="b">
+        <v>0</v>
+      </c>
+      <c r="D73" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E71" t="b">
-        <v>0</v>
-      </c>
-      <c r="F71" t="b">
-        <v>1</v>
-      </c>
-      <c r="G71" t="inlineStr">
+      <c r="E73" t="b">
+        <v>1</v>
+      </c>
+      <c r="F73" t="b">
+        <v>1</v>
+      </c>
+      <c r="G73" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "birthday month",
-      "mother's name"
+      "Birthday",
+      "Mother"
     ],
     "rows": [
       [
@@ -5352,30 +5546,30 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
+    <row r="74">
+      <c r="A74" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-4x2-26</t>
         </is>
       </c>
-      <c r="B72" t="n">
-        <v>1</v>
-      </c>
-      <c r="C72" t="b">
-        <v>0</v>
-      </c>
-      <c r="D72" t="inlineStr">
+      <c r="B74" t="n">
+        <v>1</v>
+      </c>
+      <c r="C74" t="b">
+        <v>0</v>
+      </c>
+      <c r="D74" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E72" t="b">
-        <v>1</v>
-      </c>
-      <c r="F72" t="b">
-        <v>1</v>
-      </c>
-      <c r="G72" t="inlineStr">
+      <c r="E74" t="b">
+        <v>1</v>
+      </c>
+      <c r="F74" t="b">
+        <v>1</v>
+      </c>
+      <c r="G74" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -5411,104 +5605,66 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
+    <row r="75">
+      <c r="A75" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-4x5-25</t>
         </is>
       </c>
-      <c r="B73" t="n">
-        <v>1</v>
-      </c>
-      <c r="C73" t="b">
-        <v>0</v>
-      </c>
-      <c r="D73" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E73" t="b">
-        <v>0</v>
-      </c>
-      <c r="F73" t="b">
-        <v>0</v>
-      </c>
-      <c r="G73" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "House Style",
-      "Hair Color",
-      "Child",
-      "Favorite Book Genre"
-    ],
-    "rows": [
-      [
-        "1",
-        "Arnold",
-        "victorian",
-        "red",
-        "Meredith",
-        "science fiction"
-      ],
-      [
-        "2",
-        "Eric",
-        "ranch",
-        "black",
-        "Fred",
-        "mystery"
-      ],
-      [
-        "3",
-        "Peter",
-        "craftsman",
-        "blonde",
-        "Bella",
-        "fantasy"
-      ],
-      [
-        "4",
-        "Alice",
-        "colonial",
-        "brown",
-        "Samantha",
-        "romance"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
+      <c r="B75" t="n">
+        <v>1</v>
+      </c>
+      <c r="C75" t="b">
+        <v>1</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E75" t="b">
+        <v>0</v>
+      </c>
+      <c r="F75" t="b">
+        <v>0</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Traceback (most recent call last):
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-14 21:41:45.py", line 195, in &lt;module&gt;
+    print(solve_puzzle())
+          ^^^^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-14 21:41:45.py", line 185, in solve_puzzle
+    house['Name'][0],
+    ~~~~~~~~~~~~~^^^
+IndexError: list index out of range</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-4x3-38</t>
         </is>
       </c>
-      <c r="B74" t="n">
-        <v>1</v>
-      </c>
-      <c r="C74" t="b">
-        <v>0</v>
-      </c>
-      <c r="D74" t="inlineStr">
+      <c r="B76" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" t="b">
+        <v>0</v>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E74" t="b">
-        <v>1</v>
-      </c>
-      <c r="F74" t="b">
-        <v>1</v>
-      </c>
-      <c r="G74" t="inlineStr">
+      <c r="E76" t="b">
+        <v>1</v>
+      </c>
+      <c r="F76" t="b">
+        <v>1</v>
+      </c>
+      <c r="G76" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -5549,64 +5705,82 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
+    <row r="77">
+      <c r="A77" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-2x3-31</t>
         </is>
       </c>
-      <c r="B75" t="n">
-        <v>1</v>
-      </c>
-      <c r="C75" t="b">
-        <v>0</v>
-      </c>
-      <c r="D75" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E75" t="b">
-        <v>0</v>
-      </c>
-      <c r="F75" t="b">
-        <v>0</v>
-      </c>
-      <c r="G75" t="inlineStr">
+      <c r="B77" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" t="b">
+        <v>0</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E77" t="b">
+        <v>1</v>
+      </c>
+      <c r="F77" t="b">
+        <v>1</v>
+      </c>
+      <c r="G77" t="inlineStr">
         <is>
           <t>{
   "solution": {
-    "header": [],
-    "rows": []
+    "header": [
+      "House",
+      "Name",
+      "FavoriteSport",
+      "Hobby"
+    ],
+    "rows": [
+      [
+        "1",
+        "Arnold",
+        "basketball",
+        "gardening"
+      ],
+      [
+        "2",
+        "Eric",
+        "soccer",
+        "photography"
+      ]
+    ]
   }
 }</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
+    <row r="78">
+      <c r="A78" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-2x4-23</t>
         </is>
       </c>
-      <c r="B76" t="n">
-        <v>1</v>
-      </c>
-      <c r="C76" t="b">
-        <v>0</v>
-      </c>
-      <c r="D76" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E76" t="b">
-        <v>0</v>
-      </c>
-      <c r="F76" t="b">
-        <v>0</v>
-      </c>
-      <c r="G76" t="inlineStr">
+      <c r="B78" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" t="b">
+        <v>0</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E78" t="b">
+        <v>1</v>
+      </c>
+      <c r="F78" t="b">
+        <v>1</v>
+      </c>
+      <c r="G78" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -5614,23 +5788,23 @@
       "House",
       "Name",
       "Mother",
-      "Car",
+      "CarModel",
       "Height"
     ],
     "rows": [
       [
         "1",
-        "Eric",
+        "Arnold",
         "Aniya",
         "ford f150",
-        "very short"
+        "short"
       ],
       [
         "2",
-        "Arnold",
+        "Eric",
         "Holly",
         "tesla model 3",
-        "short"
+        "very short"
       ]
     ]
   }
@@ -5638,71 +5812,76 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
+    <row r="79">
+      <c r="A79" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-5x4-31</t>
         </is>
       </c>
-      <c r="B77" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" t="b">
-        <v>0</v>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E77" t="b">
-        <v>0</v>
-      </c>
-      <c r="F77" t="b">
-        <v>0</v>
-      </c>
-      <c r="G77" t="inlineStr">
-        <is>
-          <t>{
-  "error": "No solution found"
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
+      <c r="B79" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" t="b">
+        <v>1</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E79" t="b">
+        <v>0</v>
+      </c>
+      <c r="F79" t="b">
+        <v>0</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Traceback (most recent call last):
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 02:12:51.py", line 163, in &lt;module&gt;
+    print(solve_puzzle())
+          ^^^^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 02:12:51.py", line 23, in solve_puzzle
+    solution[house] = {
+    ~~~~~~~~^^^^^^^
+KeyboardInterrupt</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-3x5-0</t>
         </is>
       </c>
-      <c r="B78" t="n">
-        <v>1</v>
-      </c>
-      <c r="C78" t="b">
-        <v>0</v>
-      </c>
-      <c r="D78" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E78" t="b">
-        <v>0</v>
-      </c>
-      <c r="F78" t="b">
-        <v>0</v>
-      </c>
-      <c r="G78" t="inlineStr">
+      <c r="B80" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" t="b">
+        <v>0</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E80" t="b">
+        <v>1</v>
+      </c>
+      <c r="F80" t="b">
+        <v>1</v>
+      </c>
+      <c r="G80" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "book genre",
-      "favorite smoothie",
-      "birthday month",
-      "height"
+      "BookGenre",
+      "Smoothie",
+      "Birthday",
+      "Height"
     ],
     "rows": [
       [
@@ -5735,39 +5914,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
+    <row r="81">
+      <c r="A81" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-2x4-4</t>
         </is>
       </c>
-      <c r="B79" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" t="b">
-        <v>0</v>
-      </c>
-      <c r="D79" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E79" t="b">
-        <v>0</v>
-      </c>
-      <c r="F79" t="b">
-        <v>0</v>
-      </c>
-      <c r="G79" t="inlineStr">
+      <c r="B81" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" t="b">
+        <v>0</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E81" t="b">
+        <v>1</v>
+      </c>
+      <c r="F81" t="b">
+        <v>1</v>
+      </c>
+      <c r="G81" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "house style",
-      "height",
-      "education"
+      "HouseStyle",
+      "Height",
+      "Education"
     ],
     "rows": [
       [
@@ -5790,93 +5969,70 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
+    <row r="82">
+      <c r="A82" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-2x3-3</t>
         </is>
       </c>
-      <c r="B80" t="n">
-        <v>1</v>
-      </c>
-      <c r="C80" t="b">
-        <v>0</v>
-      </c>
-      <c r="D80" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E80" t="b">
-        <v>0</v>
-      </c>
-      <c r="F80" t="b">
-        <v>0</v>
-      </c>
-      <c r="G80" t="inlineStr">
+      <c r="B82" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" t="b">
+        <v>0</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E82" t="b">
+        <v>1</v>
+      </c>
+      <c r="F82" t="b">
+        <v>1</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Food", "Mother"], "rows": [["1", "Arnold", "grilled cheese", "Holly"], ["2", "Eric", "pizza", "Aniya"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-3x6-19</t>
+        </is>
+      </c>
+      <c r="B83" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" t="b">
+        <v>0</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E83" t="b">
+        <v>1</v>
+      </c>
+      <c r="F83" t="b">
+        <v>1</v>
+      </c>
+      <c r="G83" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Lunch",
-      "Mother"
-    ],
-    "rows": [
-      [
-        "1",
-        "Arnold",
-        "grilled cheese",
-        "Holly"
-      ],
-      [
-        "2",
-        "Eric",
-        "pizza",
-        "Aniya"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-3x6-19</t>
-        </is>
-      </c>
-      <c r="B81" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" t="b">
-        <v>0</v>
-      </c>
-      <c r="D81" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E81" t="b">
-        <v>0</v>
-      </c>
-      <c r="F81" t="b">
-        <v>0</v>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "cigar",
-      "animal",
-      "child",
-      "book genre",
-      "phone model"
+      "Cigar",
+      "Animal",
+      "Children",
+      "BookGenre",
+      "PhoneModel"
     ],
     "rows": [
       [
@@ -5912,30 +6068,30 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
+    <row r="84">
+      <c r="A84" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-4x5-21</t>
         </is>
       </c>
-      <c r="B82" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" t="b">
-        <v>0</v>
-      </c>
-      <c r="D82" t="inlineStr">
+      <c r="B84" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" t="b">
+        <v>0</v>
+      </c>
+      <c r="D84" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E82" t="b">
-        <v>0</v>
-      </c>
-      <c r="F82" t="b">
-        <v>1</v>
-      </c>
-      <c r="G82" t="inlineStr">
+      <c r="E84" t="b">
+        <v>1</v>
+      </c>
+      <c r="F84" t="b">
+        <v>1</v>
+      </c>
+      <c r="G84" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -5943,8 +6099,8 @@
       "House",
       "Name",
       "Smoothie",
-      "Sport",
-      "Car",
+      "FavoriteSport",
+      "CarModel",
       "Flower"
     ],
     "rows": [
@@ -5986,396 +6142,225 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
+    <row r="85">
+      <c r="A85" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-6x6-29</t>
         </is>
       </c>
-      <c r="B83" t="n">
-        <v>1</v>
-      </c>
-      <c r="C83" t="b">
-        <v>0</v>
-      </c>
-      <c r="D83" t="inlineStr">
+      <c r="B85" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" t="b">
+        <v>0</v>
+      </c>
+      <c r="D85" t="inlineStr">
         <is>
           <t>Wrong plan</t>
         </is>
       </c>
-      <c r="E83" t="b">
-        <v>0</v>
-      </c>
-      <c r="F83" t="b">
-        <v>0</v>
-      </c>
-      <c r="G83" t="inlineStr">
+      <c r="E85" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" t="b">
+        <v>0</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "HouseStyle", "Food", "Vacation", "Height", "Cigar"], "rows": [["1", "Bob", "modern", "soup", "city", "short", "blends"], ["2", "Peter", "ranch", "grilled cheese", "beach", "tall", "blue master"], ["3", "Carol", "colonial", "stir fry", "cruise", "average", "dunhill"], ["4", "Eric", "craftsman", "pizza", "cultural", "very tall", "yellow monster"], ["5", "Alice", "victorian", "spaghetti", "camping", "super tall", "dunhill"], ["6", "Arnold", "craftsman", "stew", "mountain", "very tall", "yellow monster"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x2-32</t>
+        </is>
+      </c>
+      <c r="B86" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" t="b">
+        <v>0</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E86" t="b">
+        <v>1</v>
+      </c>
+      <c r="F86" t="b">
+        <v>1</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "BookGenre"], "rows": [["1", "Eric", "science fiction"], ["2", "Arnold", "mystery"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x5-9</t>
+        </is>
+      </c>
+      <c r="B87" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" t="b">
+        <v>1</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E87" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" t="b">
+        <v>0</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Traceback (most recent call last):
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-14 21:41:45.py", line 189, in &lt;module&gt;
+    print(solve_puzzle())
+          ^^^^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-14 21:41:45.py", line 21, in solve_puzzle
+    for i in range(5):
+             ^^^^^^^^
+KeyboardInterrupt</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x5-9</t>
+        </is>
+      </c>
+      <c r="B88" t="n">
+        <v>1</v>
+      </c>
+      <c r="C88" t="b">
+        <v>0</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E88" t="b">
+        <v>1</v>
+      </c>
+      <c r="F88" t="b">
+        <v>1</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "BookGenre", "Vacation", "Animal", "MusicGenre"], "rows": [["1", "Arnold", "mystery", "mountain", "cat", "rock"], ["2", "Eric", "science fiction", "beach", "horse", "pop"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x6-10</t>
+        </is>
+      </c>
+      <c r="B89" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" t="b">
+        <v>0</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E89" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" t="b">
+        <v>0</v>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>{
+  "solution": {
+    "header": [],
+    "rows": []
+  }
+}</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-6x3-26</t>
+        </is>
+      </c>
+      <c r="B90" t="n">
+        <v>1</v>
+      </c>
+      <c r="C90" t="b">
+        <v>0</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E90" t="b">
+        <v>1</v>
+      </c>
+      <c r="F90" t="b">
+        <v>1</v>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Height", "PhoneModel"], "rows": [["1", "Eric", "super tall", "huawei p50"], ["2", "Carol", "very tall", "xiaomi mi 11"], ["3", "Bob", "average", "samsung galaxy s21"], ["4", "Arnold", "tall", "google pixel 6"], ["5", "Peter", "very short", "oneplus 9"], ["6", "Alice", "short", "iphone 13"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-4x4-13</t>
+        </is>
+      </c>
+      <c r="B91" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" t="b">
+        <v>0</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E91" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" t="b">
+        <v>0</v>
+      </c>
+      <c r="G91" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "House Style",
-      "Lunch",
-      "Vacation",
-      "Height",
-      "Cigar"
-    ],
-    "rows": [
-      [
-        "1",
-        "Carol",
-        "colonial",
-        "stir fry",
-        "city",
-        "average",
-        "pall mall"
-      ],
-      [
-        "2",
-        "Bob",
-        "craftsman",
-        "pizza",
-        "cultural",
-        "very short",
-        "prince"
-      ],
-      [
-        "3",
-        "Peter",
-        "modern",
-        "grilled cheese",
-        "camping",
-        "short",
-        "blends"
-      ],
-      [
-        "4",
-        "Eric",
-        "ranch",
-        "soup",
-        "beach",
-        "tall",
-        "blue master"
-      ],
-      [
-        "5",
-        "Alice",
-        "victorian",
-        "spaghetti",
-        "mountain",
-        "very tall",
-        "yellow monster"
-      ],
-      [
-        "6",
-        "Arnold",
-        "mediterranean",
-        "stew",
-        "cruise",
-        "super ta</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x2-32</t>
-        </is>
-      </c>
-      <c r="B84" t="n">
-        <v>1</v>
-      </c>
-      <c r="C84" t="b">
-        <v>0</v>
-      </c>
-      <c r="D84" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E84" t="b">
-        <v>0</v>
-      </c>
-      <c r="F84" t="b">
-        <v>0</v>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "Favorite book genre"
-    ],
-    "rows": [
-      [
-        "1",
-        "Eric",
-        "science fiction"
-      ],
-      [
-        "2",
-        "Arnold",
-        "mystery"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x5-9</t>
-        </is>
-      </c>
-      <c r="B85" t="n">
-        <v>1</v>
-      </c>
-      <c r="C85" t="b">
-        <v>0</v>
-      </c>
-      <c r="D85" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E85" t="b">
-        <v>0</v>
-      </c>
-      <c r="F85" t="b">
-        <v>0</v>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "Drink",
-      "Color",
-      "Flower",
-      "Hobby"
-    ],
-    "rows": [
-      [
-        "1",
-        "Eric",
-        "root beer",
-        "yellow",
-        "carnations",
-        "gardening"
-      ],
-      [
-        "2",
-        "Arnold",
-        "tea",
-        "white",
-        "roses",
-        "photography"
-      ],
-      [
-        "3",
-        "Peter",
-        "water",
-        "red",
-        "daffodils",
-        "knitting"
-      ],
-      [
-        "4",
-        "Alice",
-        "milk",
-        "blue",
-        "tulips",
-        "cooking"
-      ],
-      [
-        "5",
-        "Bob",
-        "coffee",
-        "green",
-        "lilies",
-        "painting"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x5-9</t>
-        </is>
-      </c>
-      <c r="B86" t="n">
-        <v>1</v>
-      </c>
-      <c r="C86" t="b">
-        <v>0</v>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E86" t="b">
-        <v>0</v>
-      </c>
-      <c r="F86" t="b">
-        <v>0</v>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "Book Genre",
-      "Vacation",
-      "Animal",
-      "Music Genre"
-    ],
-    "rows": [
-      [
-        "1",
-        "Arnold",
-        "mystery",
-        "mountain",
-        "cat",
-        "rock"
-      ],
-      [
-        "2",
-        "Eric",
-        "science fiction",
-        "beach",
-        "horse",
-        "pop"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-6x3-26</t>
-        </is>
-      </c>
-      <c r="B87" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" t="b">
-        <v>0</v>
-      </c>
-      <c r="D87" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E87" t="b">
-        <v>0</v>
-      </c>
-      <c r="F87" t="b">
-        <v>1</v>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "height",
-      "phone"
-    ],
-    "rows": [
-      [
-        "1",
-        "Eric",
-        "super tall",
-        "huawei p50"
-      ],
-      [
-        "2",
-        "Carol",
-        "very tall",
-        "xiaomi mi 11"
-      ],
-      [
-        "3",
-        "Bob",
-        "average",
-        "samsung galaxy s21"
-      ],
-      [
-        "4",
-        "Arnold",
-        "tall",
-        "google pixel 6"
-      ],
-      [
-        "5",
-        "Peter",
-        "very short",
-        "oneplus 9"
-      ],
-      [
-        "6",
-        "Alice",
-        "short",
-        "iphone 13"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-4x4-13</t>
-        </is>
-      </c>
-      <c r="B88" t="n">
-        <v>1</v>
-      </c>
-      <c r="C88" t="b">
-        <v>0</v>
-      </c>
-      <c r="D88" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E88" t="b">
-        <v>0</v>
-      </c>
-      <c r="F88" t="b">
-        <v>0</v>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "cigar",
-      "sport",
-      "drink"
+      "Cigar",
+      "FavoriteSport",
+      "Drink"
     ],
     "rows": [
       [
@@ -6412,30 +6397,30 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
+    <row r="92">
+      <c r="A92" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-4x3-39</t>
         </is>
       </c>
-      <c r="B89" t="n">
-        <v>1</v>
-      </c>
-      <c r="C89" t="b">
-        <v>0</v>
-      </c>
-      <c r="D89" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E89" t="b">
-        <v>0</v>
-      </c>
-      <c r="F89" t="b">
-        <v>0</v>
-      </c>
-      <c r="G89" t="inlineStr">
+      <c r="B92" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" t="b">
+        <v>0</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E92" t="b">
+        <v>1</v>
+      </c>
+      <c r="F92" t="b">
+        <v>1</v>
+      </c>
+      <c r="G92" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -6443,32 +6428,32 @@
       "House",
       "Name",
       "HairColor",
-      "Sport"
+      "FavoriteSport"
     ],
     "rows": [
       [
         "1",
-        "Eric",
-        "blonde",
+        "Arnold",
+        "brown",
         "basketball"
       ],
       [
         "2",
         "Alice",
-        "brown",
+        "red",
         "swimming"
       ],
       [
         "3",
-        "Arnold",
-        "red",
-        "soccer"
-      ],
-      [
-        "4",
         "Peter",
         "black",
         "tennis"
+      ],
+      [
+        "4",
+        "Eric",
+        "blonde",
+        "soccer"
       ]
     ]
   }
@@ -6476,87 +6461,116 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
+    <row r="93">
+      <c r="A93" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-5x6-37</t>
         </is>
       </c>
-      <c r="B90" t="n">
-        <v>1</v>
-      </c>
-      <c r="C90" t="b">
-        <v>0</v>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E90" t="b">
-        <v>0</v>
-      </c>
-      <c r="F90" t="b">
-        <v>0</v>
-      </c>
-      <c r="G90" t="inlineStr">
+      <c r="B93" t="n">
+        <v>1</v>
+      </c>
+      <c r="C93" t="b">
+        <v>1</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>Error</t>
+        </is>
+      </c>
+      <c r="E93" t="b">
+        <v>0</v>
+      </c>
+      <c r="F93" t="b">
+        <v>0</v>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Traceback (most recent call last):
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:28:58.py", line 288, in &lt;module&gt;
+    print(solve_puzzle())
+          ^^^^^^^^^^^^^^
+  File "/local-ssd/rma336/calendar-planning/source/generated_code_zebralogic_2025-08-15 01:28:58.py", line 279, in solve_puzzle
+    hobby = possibilities[i]['Hobby'][0]
+            ~~~~~~~~~~~~~~~~~~~~~~~~~^^^
+IndexError: list index out of range</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x2-14</t>
+        </is>
+      </c>
+      <c r="B94" t="n">
+        <v>1</v>
+      </c>
+      <c r="C94" t="b">
+        <v>0</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E94" t="b">
+        <v>1</v>
+      </c>
+      <c r="F94" t="b">
+        <v>1</v>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "Food"], "rows": [["1", "Eric", "grilled cheese"], ["2", "Arnold", "pizza"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-2x3-32</t>
+        </is>
+      </c>
+      <c r="B95" t="n">
+        <v>1</v>
+      </c>
+      <c r="C95" t="b">
+        <v>0</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E95" t="b">
+        <v>1</v>
+      </c>
+      <c r="F95" t="b">
+        <v>1</v>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "Hobby",
-      "Sport",
-      "House Style",
-      "Child",
-      "Height"
+      "Birthday",
+      "Color"
     ],
     "rows": [
       [
         "1",
+        "Arnold",
+        "april",
+        "red"
+      ],
+      [
+        "2",
         "Eric",
-        "knitting",
-        "soccer",
-        "craftsman",
-        "Meredith",
-        "average"
-      ],
-      [
-        "2",
-        "Alice",
-        "gardening",
-        "swimming",
-        "ranch",
-        "Timothy",
-        "tall"
-      ],
-      [
-        "3",
-        "Arnold",
-        "cooking",
-        "tennis",
-        "modern",
-        "Bella",
-        "very short"
-      ],
-      [
-        "4",
-        "Peter",
-        "photography",
-        "baseball",
-        "colonial",
-        "Bella",
-        "very tall"
-      ],
-      [
-        "5",
-        "Bob",
-        "painting",
-        "basketball",
-        "victorian",
-        "Fred",
-        "short"
+        "sept",
+        "yellow"
       ]
     ]
   }
@@ -6564,108 +6578,30 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x2-14</t>
-        </is>
-      </c>
-      <c r="B91" t="n">
-        <v>1</v>
-      </c>
-      <c r="C91" t="b">
-        <v>0</v>
-      </c>
-      <c r="D91" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E91" t="b">
-        <v>0</v>
-      </c>
-      <c r="F91" t="b">
-        <v>0</v>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "lunch"
-    ],
-    "rows": [
-      [
-        "1",
-        "Eric",
-        "grilled cheese"
-      ],
-      [
-        "2",
-        "Arnold",
-        "pizza"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-2x3-32</t>
-        </is>
-      </c>
-      <c r="B92" t="n">
-        <v>1</v>
-      </c>
-      <c r="C92" t="b">
-        <v>0</v>
-      </c>
-      <c r="D92" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E92" t="b">
-        <v>0</v>
-      </c>
-      <c r="F92" t="b">
-        <v>0</v>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>{"solution": {"header": [], "rows": []}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
+    <row r="96">
+      <c r="A96" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-2x2-25</t>
         </is>
       </c>
-      <c r="B93" t="n">
-        <v>1</v>
-      </c>
-      <c r="C93" t="b">
-        <v>0</v>
-      </c>
-      <c r="D93" t="inlineStr">
+      <c r="B96" t="n">
+        <v>1</v>
+      </c>
+      <c r="C96" t="b">
+        <v>0</v>
+      </c>
+      <c r="D96" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E93" t="b">
-        <v>1</v>
-      </c>
-      <c r="F93" t="b">
-        <v>1</v>
-      </c>
-      <c r="G93" t="inlineStr">
+      <c r="E96" t="b">
+        <v>1</v>
+      </c>
+      <c r="F96" t="b">
+        <v>1</v>
+      </c>
+      <c r="G96" t="inlineStr">
         <is>
           <t>{
   "solution": {
@@ -6691,40 +6627,40 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
+    <row r="97">
+      <c r="A97" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-4x5-6</t>
         </is>
       </c>
-      <c r="B94" t="n">
-        <v>1</v>
-      </c>
-      <c r="C94" t="b">
-        <v>0</v>
-      </c>
-      <c r="D94" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E94" t="b">
-        <v>0</v>
-      </c>
-      <c r="F94" t="b">
-        <v>0</v>
-      </c>
-      <c r="G94" t="inlineStr">
+      <c r="B97" t="n">
+        <v>1</v>
+      </c>
+      <c r="C97" t="b">
+        <v>0</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E97" t="b">
+        <v>1</v>
+      </c>
+      <c r="F97" t="b">
+        <v>1</v>
+      </c>
+      <c r="G97" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "education",
-      "music genre",
-      "color",
-      "flower"
+      "Education",
+      "MusicGenre",
+      "Color",
+      "Flower"
     ],
     "rows": [
       [
@@ -6765,40 +6701,40 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
+    <row r="98">
+      <c r="A98" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-3x5-12</t>
         </is>
       </c>
-      <c r="B95" t="n">
-        <v>1</v>
-      </c>
-      <c r="C95" t="b">
-        <v>0</v>
-      </c>
-      <c r="D95" t="inlineStr">
+      <c r="B98" t="n">
+        <v>1</v>
+      </c>
+      <c r="C98" t="b">
+        <v>0</v>
+      </c>
+      <c r="D98" t="inlineStr">
         <is>
           <t>Correct</t>
         </is>
       </c>
-      <c r="E95" t="b">
-        <v>0</v>
-      </c>
-      <c r="F95" t="b">
-        <v>1</v>
-      </c>
-      <c r="G95" t="inlineStr">
+      <c r="E98" t="b">
+        <v>1</v>
+      </c>
+      <c r="F98" t="b">
+        <v>1</v>
+      </c>
+      <c r="G98" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "cigar",
-      "hobby",
-      "education",
-      "drink"
+      "Cigar",
+      "Hobby",
+      "Education",
+      "Drink"
     ],
     "rows": [
       [
@@ -6831,41 +6767,41 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
+    <row r="99">
+      <c r="A99" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-2x6-1</t>
         </is>
       </c>
-      <c r="B96" t="n">
-        <v>1</v>
-      </c>
-      <c r="C96" t="b">
-        <v>0</v>
-      </c>
-      <c r="D96" t="inlineStr">
-        <is>
-          <t>Wrong plan</t>
-        </is>
-      </c>
-      <c r="E96" t="b">
-        <v>0</v>
-      </c>
-      <c r="F96" t="b">
-        <v>0</v>
-      </c>
-      <c r="G96" t="inlineStr">
+      <c r="B99" t="n">
+        <v>1</v>
+      </c>
+      <c r="C99" t="b">
+        <v>0</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>Correct</t>
+        </is>
+      </c>
+      <c r="E99" t="b">
+        <v>1</v>
+      </c>
+      <c r="F99" t="b">
+        <v>1</v>
+      </c>
+      <c r="G99" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "sport",
-      "hair color",
-      "height",
-      "smoothie",
-      "flower"
+      "FavoriteSport",
+      "HairColor",
+      "Height",
+      "Smoothie",
+      "Flower"
     ],
     "rows": [
       [
@@ -6892,108 +6828,68 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
+    <row r="100">
+      <c r="A100" t="inlineStr">
         <is>
           <t>zebralogic_example_lgp-test-4x4-21</t>
         </is>
       </c>
-      <c r="B97" t="n">
-        <v>1</v>
-      </c>
-      <c r="C97" t="b">
-        <v>0</v>
-      </c>
-      <c r="D97" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E97" t="b">
-        <v>0</v>
-      </c>
-      <c r="F97" t="b">
-        <v>1</v>
-      </c>
-      <c r="G97" t="inlineStr">
+      <c r="B100" t="n">
+        <v>1</v>
+      </c>
+      <c r="C100" t="b">
+        <v>0</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E100" t="b">
+        <v>0</v>
+      </c>
+      <c r="F100" t="b">
+        <v>0</v>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>{"solution": {"header": ["House", "Name", "CarModel", "Birthday", "Hobby"], "rows": [["1", "Peter", "toyota camry", "jan", "painting"], ["2", "Eric", "tesla model 3", "april", "cooking"], ["3", "Alice", "honda civic", "sept", "gardening"], ["4", "Arnold", "ford f150", "feb", "photography"]]}}</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>zebralogic_example_lgp-test-5x4-7</t>
+        </is>
+      </c>
+      <c r="B101" t="n">
+        <v>1</v>
+      </c>
+      <c r="C101" t="b">
+        <v>0</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>Wrong plan</t>
+        </is>
+      </c>
+      <c r="E101" t="b">
+        <v>1</v>
+      </c>
+      <c r="F101" t="b">
+        <v>0</v>
+      </c>
+      <c r="G101" t="inlineStr">
         <is>
           <t>{
   "solution": {
     "header": [
       "House",
       "Name",
-      "car",
-      "birthday month",
-      "hobby"
-    ],
-    "rows": [
-      [
-        "1",
-        "Alice",
-        "honda civic",
-        "sept",
-        "photography"
-      ],
-      [
-        "2",
-        "Arnold",
-        "tesla model 3",
-        "april",
-        "painting"
-      ],
-      [
-        "3",
-        "Eric",
-        "ford f150",
-        "feb",
-        "cooking"
-      ],
-      [
-        "4",
-        "Peter",
-        "toyota camry",
-        "jan",
-        "gardening"
-      ]
-    ]
-  }
-}</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>zebralogic_example_lgp-test-5x4-7</t>
-        </is>
-      </c>
-      <c r="B98" t="n">
-        <v>1</v>
-      </c>
-      <c r="C98" t="b">
-        <v>0</v>
-      </c>
-      <c r="D98" t="inlineStr">
-        <is>
-          <t>Correct</t>
-        </is>
-      </c>
-      <c r="E98" t="b">
-        <v>0</v>
-      </c>
-      <c r="F98" t="b">
-        <v>1</v>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>{
-  "solution": {
-    "header": [
-      "House",
-      "Name",
-      "smoothie",
-      "animal",
-      "nationality"
+      "Smoothie",
+      "Animal",
+      "Nationality"
     ],
     "rows": [
       [
